--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
@@ -748,103 +748,101 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">227
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">281
 </t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
-</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">561
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -868,8 +866,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -899,18 +896,18 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+          <t>314</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -940,7 +937,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -952,7 +949,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -970,7 +967,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
@@ -982,7 +979,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -994,13 +991,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1030,8 +1027,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1097,7 +1093,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -1121,7 +1117,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">9885
 </t>
         </is>
       </c>
@@ -1145,7 +1141,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1173,9 +1169,9 @@
 </t>
         </is>
       </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
+      <c r="X6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -1187,7 +1183,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -1224,127 +1220,126 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">021
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">729
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">946
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1375,132 +1370,131 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">543
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t xml:space="preserve">8706
+</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">3080
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="V8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">395
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">3891
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1531,125 +1525,131 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">216
+</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">9274
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">2 066
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
-</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308 10
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">240
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2729
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1680,128 +1680,131 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">771
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">088
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
-</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t xml:space="preserve">5635
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1820,90 +1823,89 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4203
+          <t xml:space="preserve">4263
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9332
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1915,48 +1917,49 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -1981,137 +1984,136 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t xml:space="preserve">970
+</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">672
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
+          <t>238</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -2130,145 +2132,145 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">23621
+</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2925
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9980
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2287,145 +2289,145 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">253
+1
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">028
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -2456,133 +2458,133 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">4960
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">427
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">763
+</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">365
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">758
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
+          <t xml:space="preserve">3861
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">424
+</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2600,138 +2602,143 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>53041</t>
+          <t xml:space="preserve">15308
+</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15242
-</t>
+          <t>0545</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
+          <t xml:space="preserve">1992
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">1069
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0289
+          <t xml:space="preserve">2066
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">019
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>097</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
+          <t xml:space="preserve">36065
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">280
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
+          <t xml:space="preserve">7256
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2750,8 +2757,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
-</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2762,128 +2768,127 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>519</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">394
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">067
+</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">251
 </t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">668
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -2902,89 +2907,89 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3365
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">36
+</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">421
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">980
+</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -2996,48 +3001,48 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t xml:space="preserve">885
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3056,145 +3061,145 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">421
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">263
 </t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">605
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3212,67 +3217,65 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">884
-</t>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3284,25 +3287,25 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">10068
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3314,43 +3317,42 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
-</t>
+          <t>634</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t>514</t>
+          <t xml:space="preserve">354
+</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3368,66 +3370,66 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">2949
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">312
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">61 1
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -3445,66 +3447,68 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t xml:space="preserve">240
+</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3522,145 +3526,140 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">554
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>3155</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>984</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4940
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">13
 </t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">000
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">529
+</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">3200
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">796
+</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">783
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4420
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3679,142 +3678,143 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150519
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">3 2
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>651</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9728
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12529
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19116
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18993
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t xml:space="preserve">281
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3833,125 +3833,139 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>3516</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">74
+15156
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">4
 </t>
         </is>
       </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3970,45 +3984,54 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">261
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -4017,13 +4040,13 @@
 </t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">398
+</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">229
 </t>
@@ -4035,14 +4058,23 @@
 </t>
         </is>
       </c>
-      <c r="P25" s="3" t="n"/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="n"/>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">261
@@ -4051,17 +4083,18 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>236</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4079,14 +4112,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">9526
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4108,39 +4140,39 @@
 </t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6861
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -4152,19 +4184,19 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -4182,7 +4214,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4194,7 +4226,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -4210,15 +4242,15 @@
 </t>
         </is>
       </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">066
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -4230,19 +4262,19 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4260,13 +4292,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>329</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4275,39 +4307,39 @@
 </t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">861
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4317,7 +4349,7 @@
 </t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
 </t>
@@ -4331,13 +4363,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
@@ -4379,8 +4410,7 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>655</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
@@ -4391,14 +4421,12 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4422,8 +4450,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4434,25 +4461,24 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4464,19 +4490,18 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2201
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+          <t>181</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -4488,19 +4513,19 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -4524,7 +4549,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -4548,13 +4573,12 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4577,16 +4601,15 @@
 </t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4597,19 +4620,18 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
@@ -4621,7 +4643,8 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>684</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -4650,7 +4673,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -4674,7 +4697,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -4704,12 +4727,12 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -4734,76 +4757,79 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15065
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t xml:space="preserve">9961
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">1728
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4895
+          <t xml:space="preserve">4295
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4815,12 +4841,14 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t xml:space="preserve">210
+</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -4837,29 +4865,32 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>531</t>
+          <t xml:space="preserve">153
+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">26
+4
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -4882,39 +4913,39 @@
 </t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">313
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4924,16 +4955,19 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -4945,7 +4979,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">9789
 </t>
         </is>
       </c>
@@ -4955,27 +4989,27 @@
 </t>
         </is>
       </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">842
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">391
+</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">6 89
 </t>
         </is>
       </c>
@@ -4993,26 +5027,27 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">1141
+22
+171971191 7
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5036,81 +5071,86 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">290
 </t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n"/>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -5119,13 +5159,14 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t xml:space="preserve">698
+</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5134,9 +5175,9 @@
 </t>
         </is>
       </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
@@ -5154,13 +5195,14 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">1717177
+23
+83
 </t>
         </is>
       </c>
@@ -5185,7 +5227,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
@@ -5195,45 +5237,45 @@
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5251,13 +5293,13 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9808
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -5275,7 +5317,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -5310,12 +5352,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>287</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5333,12 +5376,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -5348,44 +5391,49 @@
 </t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">439
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n"/>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0612
 </t>
         </is>
       </c>
@@ -5397,19 +5445,19 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">9808
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2 20
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -5427,7 +5475,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
@@ -5437,9 +5485,9 @@
 </t>
         </is>
       </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
@@ -5463,8 +5511,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5488,7 +5535,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5506,49 +5553,48 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">0 6
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">13 72
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -5596,7 +5642,8 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>663</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
@@ -5619,7 +5666,8 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5641,9 +5689,9 @@
 </t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
@@ -5653,27 +5701,28 @@
 </t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">439
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">222725
+1142811042
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">0 6
 </t>
         </is>
       </c>
@@ -5685,7 +5734,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">13 72
 </t>
         </is>
       </c>
@@ -5703,19 +5752,19 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
@@ -5745,13 +5794,12 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
@@ -5763,17 +5811,19 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -5792,24 +5842,25 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>00401</t>
+          <t xml:space="preserve">0600
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -5826,39 +5877,44 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">58
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>12034446</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>0444</t>
+          <t xml:space="preserve">777
+22
+7
+</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
+          <t xml:space="preserve">4250
 </t>
         </is>
       </c>
@@ -5870,19 +5926,19 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
+          <t xml:space="preserve">13341
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112879
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
@@ -5906,16 +5962,11 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4160
@@ -5924,7 +5975,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -5955,8 +6006,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -5967,7 +6017,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -5979,7 +6029,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -5998,8 +6048,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -6016,11 +6065,16 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="n"/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">236
@@ -6029,13 +6083,13 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
@@ -6053,18 +6107,19 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>465</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">83248
 </t>
         </is>
       </c>
@@ -6089,20 +6144,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -6117,7 +6171,7 @@
 </t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -6125,29 +6179,35 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">7 29
+15
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n"/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">990
@@ -6156,66 +6216,63 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">427
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">061
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6233,143 +6290,139 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">066
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>988</t>
+          <t xml:space="preserve">9906
+</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">705
+          <t xml:space="preserve">654
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6388,144 +6441,142 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
+111
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -6544,35 +6595,34 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">369
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -6580,102 +6630,108 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">528
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106182
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="inlineStr">
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6693,12 +6749,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>77797</t>
+          <t xml:space="preserve">3116
+</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -6716,26 +6773,31 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="n"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6752,10 +6814,15 @@
 </t>
         </is>
       </c>
-      <c r="O43" s="3" t="n"/>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -6765,17 +6832,27 @@
 </t>
         </is>
       </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6785,18 +6862,26 @@
 </t>
         </is>
       </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6814,90 +6899,135 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>77797</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>9346</t>
+          <t xml:space="preserve">3116
+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">715
+</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">797
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54652
+</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">42424
+211
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">038
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4918
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+111562
+</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="n"/>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">64
+</t>
         </is>
       </c>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">24612
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+          <t xml:space="preserve">463
+</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3733
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">781
+</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7260
+</t>
+        </is>
+      </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">797
+</t>
+        </is>
+      </c>
+      <c r="X44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32423
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6913,36 +7043,38 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">14534
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t xml:space="preserve">305
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">7797
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t xml:space="preserve">936
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6951,65 +7083,67 @@
 </t>
         </is>
       </c>
-      <c r="J45" s="3" t="n"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
       <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t>4942</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1463
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>645</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">781
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">3414
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">717
 </t>
         </is>
       </c>
@@ -7027,13 +7161,13 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">32423
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">383
 </t>
         </is>
       </c>
@@ -7050,12 +7184,27 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2907
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">305
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -7065,7 +7214,7 @@
 </t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">187
 </t>
@@ -7073,7 +7222,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -7083,62 +7232,99 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="S46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">324
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
@@ -743,12 +743,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -764,35 +764,37 @@
 </t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>66</t>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">227
 </t>
@@ -806,47 +808,47 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
+          <t xml:space="preserve">0975
+</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">017
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">330
 </t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12811
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
+          <t xml:space="preserve">1561
+</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -858,7 +860,7 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="X4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
@@ -866,12 +868,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t xml:space="preserve">1743
+</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
@@ -896,18 +899,18 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">608
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
+          <t>341</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -937,17 +940,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
@@ -955,23 +958,22 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -979,11 +981,11 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
@@ -991,17 +993,17 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
@@ -1013,7 +1015,7 @@
 </t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="X5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -1021,13 +1023,14 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1920
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1045,7 +1048,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">123680
 </t>
         </is>
       </c>
@@ -1061,15 +1064,15 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2063
+</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4103
 </t>
         </is>
       </c>
@@ -1081,35 +1084,30 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">251
 </t>
@@ -1117,23 +1115,23 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9885
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">314
 </t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -1141,13 +1139,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -1163,7 +1160,7 @@
 </t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -1171,19 +1168,19 @@
       </c>
       <c r="X6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1218,128 +1215,127 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>9444</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>345</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0113
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">19808
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3119
+</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1595
+</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="X7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -1358,7 +1354,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">193680
 </t>
         </is>
       </c>
@@ -1368,133 +1364,135 @@
 </t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>3445</t>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">417
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">019
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">282
 </t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8706
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>3446</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">578
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3080
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">961
-</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">352
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">395
-</t>
-        </is>
-      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1513,143 +1511,85 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1617
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">171836
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9274
+          <t xml:space="preserve">4870
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 066
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>3446</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">13715
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">9080
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1901
+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" s="3" t="n"/>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2729
+          <t xml:space="preserve">10325
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">13891
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1668,7 +1608,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">23567
 </t>
         </is>
       </c>
@@ -1680,131 +1620,128 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">771
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">088
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1974
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1616
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">240
 </t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5635
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1823,89 +1760,90 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4263
-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>233</t>
+          <t>4531</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">933
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711
+</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -1915,51 +1853,51 @@
 </t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1563
+</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6551
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">704
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1978,142 +1916,145 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">1418240
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">328
+</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2203
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19580
+</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">672
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">629
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">7132
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2132,145 +2073,140 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23621
+          <t xml:space="preserve">12301
 </t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2925
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">2291
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">83
+</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n"/>
       <c r="Q13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">2291
+</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1679
+</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2289,145 +2225,144 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">18214
+</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0195
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-1
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">028
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">606
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">411
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2450,7 +2385,7 @@
 </t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">314
 </t>
@@ -2458,132 +2393,132 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>945</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">029
-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0080
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4960
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">427
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">763
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">365
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2600,38 +2535,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15308
-</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>0545</t>
-        </is>
-      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1992
+          <t xml:space="preserve">997
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
+          <t xml:space="preserve">1545
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
@@ -2643,102 +2569,63 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2066
-</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1864
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">14900
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36065
-</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1524
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">13310
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1763
+</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7256
+          <t xml:space="preserve">13861
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">423
 </t>
         </is>
       </c>
@@ -2757,7 +2644,8 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t xml:space="preserve">3062
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2768,127 +2656,123 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">394
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">1980
+</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">067
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="n"/>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">280
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">17172
+</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
@@ -2907,142 +2791,145 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3365
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>463</t>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0084
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">253
 </t>
         </is>
       </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1580
+</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">011
+</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2298
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">1776
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -3061,145 +2948,146 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">13262
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">421
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1885
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3217,95 +3105,91 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">12990
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
+          <t>911</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10068
-</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2384
 </t>
         </is>
       </c>
@@ -3317,41 +3201,43 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">1716
+</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">263
 </t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">424
-</t>
-        </is>
-      </c>
-      <c r="X20" s="3" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3370,144 +3256,139 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
+          <t xml:space="preserve">13575
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61 1
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">10010
+</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1631
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1841
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3526,140 +3407,139 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">12949
+</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">554
-</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>961</t>
+          <t xml:space="preserve">5312
+</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>984</t>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
+</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="Q22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
-        </is>
-      </c>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">783
-</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2165
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3676,145 +3556,82 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3220
-</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1984
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4940
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12529
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">13200
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1796
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="n"/>
+      <c r="W23" s="3" t="n"/>
+      <c r="X23" s="3" t="n"/>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3833,139 +3650,133 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">3220
+</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">092
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9881</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>3516</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-15156
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1640
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">553
 </t>
         </is>
       </c>
@@ -3984,13 +3795,13 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
@@ -4002,123 +3813,121 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>1944</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">261
 </t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">932
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9526
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4136,67 +3945,61 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">23450
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6861
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -4208,7 +4011,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
@@ -4224,7 +4027,7 @@
 </t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
+      <c r="R26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -4242,19 +4045,19 @@
 </t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">066
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">236
 </t>
@@ -4262,19 +4065,19 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>621</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1743
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4292,54 +4095,48 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">24182
+</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4355,7 +4152,7 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -4363,12 +4160,13 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t xml:space="preserve">1990
+</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">062
+          <t xml:space="preserve">042
 </t>
         </is>
       </c>
@@ -4378,13 +4176,13 @@
 </t>
         </is>
       </c>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="R27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="S27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
@@ -4392,7 +4190,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
@@ -4408,12 +4206,13 @@
 </t>
         </is>
       </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">955
+</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">302
 </t>
@@ -4421,12 +4220,14 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1742
+</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">1105
+</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4448,37 +4249,38 @@
 </t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>1908</t>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -4490,7 +4292,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>126</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4499,33 +4301,32 @@
 </t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -4535,7 +4336,7 @@
 </t>
         </is>
       </c>
-      <c r="S28" s="3" t="inlineStr">
+      <c r="S28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">289
 </t>
@@ -4543,42 +4344,43 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2244
+</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
+      <c r="X28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2603
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t xml:space="preserve">1860
+</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4597,22 +4399,23 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1402
-</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">585
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>803</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -4620,30 +4423,31 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4653,13 +4457,13 @@
 </t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
+      <c r="M29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">254
 </t>
@@ -4667,23 +4471,22 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
+      <c r="R29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -4697,7 +4500,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
@@ -4707,19 +4510,19 @@
 </t>
         </is>
       </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">350
+</t>
+        </is>
+      </c>
+      <c r="W29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="X29" s="3" t="inlineStr">
+      <c r="X29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -4727,12 +4530,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t xml:space="preserve">1818
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4749,148 +4553,82 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13635
-</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9961
-</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">5069
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1922
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1721
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1728
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295
+          <t xml:space="preserve">14895
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1455
-</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="n"/>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
+          <t xml:space="preserve">13445
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1688
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="n"/>
+      <c r="W30" s="3" t="n"/>
+      <c r="X30" s="3" t="n"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">14115
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -4913,39 +4651,39 @@
 </t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -4955,23 +4693,20 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">236
 </t>
@@ -4979,75 +4714,72 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9789
+          <t xml:space="preserve">1979
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">042
+</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 89
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
+          <t>2551</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="X31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2067
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-22
-171971191 7
-</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">162
+</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5065,13 +4797,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">12635
+</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -5081,7 +4813,7 @@
 </t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -5089,46 +4821,42 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
+      <c r="N32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -5136,13 +4864,13 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -5151,21 +4879,21 @@
 </t>
         </is>
       </c>
-      <c r="R32" s="3" t="inlineStr">
+      <c r="R32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">1698
 </t>
         </is>
       </c>
@@ -5177,32 +4905,31 @@
       </c>
       <c r="V32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+      <c r="X32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1811
+</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1717177
-23
-83
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5221,13 +4948,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -5237,45 +4964,40 @@
 </t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5285,7 +5007,7 @@
 </t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="N33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -5293,16 +5015,11 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n"/>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
@@ -5315,49 +5032,51 @@
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="W33" s="3" t="inlineStr">
+      <c r="W33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
+      <c r="X33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>287</t>
+          <t xml:space="preserve">1918
+</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5376,12 +5095,13 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">11178
+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
@@ -5391,49 +5111,46 @@
 </t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">439
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1678
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0612
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -5445,23 +5162,23 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 20
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -5475,7 +5192,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
@@ -5487,11 +5204,11 @@
       </c>
       <c r="V34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
-</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="inlineStr">
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
@@ -5499,19 +5216,20 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">1625
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5529,13 +5247,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
-</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">12844
+</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">095
 </t>
         </is>
       </c>
@@ -5545,7 +5263,7 @@
 </t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -5553,60 +5271,54 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 6
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 72
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5616,13 +5328,13 @@
 </t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr">
+      <c r="R35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="S35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -5630,7 +5342,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">2754
 </t>
         </is>
       </c>
@@ -5654,7 +5366,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -5666,7 +5378,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5685,13 +5397,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5701,40 +5413,39 @@
 </t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">439
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222725
-1142811042
+          <t xml:space="preserve">725
+</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 6
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 72
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -5750,36 +5461,36 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">064
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
@@ -5788,42 +5499,43 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">948
 </t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">414
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5842,30 +5554,16 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0600
-</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8264
+</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">1429
 </t>
         </is>
       </c>
@@ -5877,47 +5575,26 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>10344</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-22
-7
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4250
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10
@@ -5926,22 +5603,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13341
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1179
-</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">863
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1331
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="n"/>
+      <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3936
@@ -5950,32 +5617,22 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="n"/>
+      <c r="W37" s="3" t="n"/>
       <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
+          <t xml:space="preserve">14160
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5994,7 +5651,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">1633
 </t>
         </is>
       </c>
@@ -6006,7 +5663,8 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -6017,28 +5675,23 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -6048,7 +5701,8 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -6059,17 +5713,17 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
@@ -6081,37 +5735,37 @@
 </t>
         </is>
       </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">735
+      <c r="S38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9273
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
+          <t xml:space="preserve">787
+</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8111
+</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="X38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -6119,7 +5773,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83248
+          <t xml:space="preserve">18392
 </t>
         </is>
       </c>
@@ -6144,19 +5798,20 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">367
-</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>93</t>
+          <t xml:space="preserve">3325
+</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">907
+</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">693
+</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -6171,58 +5826,64 @@
 </t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n"/>
+          <t xml:space="preserve">935
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 29
-15
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>101</t>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1307
+</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -6233,45 +5894,49 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>893</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>6661</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">427
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t>612</t>
+          <t xml:space="preserve">1665
+</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="X39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">729
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">061
+          <t xml:space="preserve">1061
 </t>
         </is>
       </c>
@@ -6290,29 +5955,29 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
+          <t xml:space="preserve">2781
+</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">308
 </t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">066
-</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2297
+</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">102
 </t>
@@ -6326,30 +5991,34 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n"/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
+          <t>74</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -6357,23 +6026,23 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9906
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">367
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
+</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">253
 </t>
@@ -6387,7 +6056,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">1654
 </t>
         </is>
       </c>
@@ -6397,7 +6066,7 @@
 </t>
         </is>
       </c>
-      <c r="V40" s="3" t="inlineStr">
+      <c r="V40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
@@ -6409,7 +6078,7 @@
 </t>
         </is>
       </c>
-      <c r="X40" s="3" t="inlineStr">
+      <c r="X40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">273
 </t>
@@ -6417,7 +6086,8 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">722
+</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
@@ -6447,12 +6117,14 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>268</t>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -6463,7 +6135,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -6473,67 +6145,67 @@
 </t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1938
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">15
 </t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-111
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>988</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">093
+</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S41" s="3" t="inlineStr">
+      <c r="S41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">287
 </t>
@@ -6541,42 +6213,42 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">7205
 </t>
         </is>
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="X41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">18411
+</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -6601,13 +6273,14 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">369
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6622,73 +6295,73 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106182
+          <t xml:space="preserve">16000
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">309
 </t>
         </is>
       </c>
-      <c r="R42" s="3" t="inlineStr">
+      <c r="R42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
+      <c r="S42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">276
 </t>
@@ -6696,19 +6369,20 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t xml:space="preserve">1620
+</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2071
+</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
@@ -6717,20 +6391,21 @@
 </t>
         </is>
       </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
+      <c r="X42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2393
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1818
+</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6749,13 +6424,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">23116
+</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -6777,27 +6452,22 @@
 </t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+      <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -6807,8 +6477,13 @@
 </t>
         </is>
       </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="inlineStr">
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -6816,29 +6491,29 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
+      <c r="R43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="S43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
@@ -6846,7 +6521,7 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6858,30 +6533,31 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>354</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
+          <t xml:space="preserve">1843
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6897,136 +6573,29 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3116
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">715
-</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">797
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54652
-</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42424
-211
-</t>
-        </is>
-      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-111562
-</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
-</t>
-        </is>
-      </c>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
       <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">463
-</t>
-        </is>
-      </c>
-      <c r="R44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3733
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">781
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7260
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">797
-</t>
-        </is>
-      </c>
-      <c r="X44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">518
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32423
-</t>
-        </is>
-      </c>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
+      <c r="R44" s="3" t="n"/>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n"/>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="n"/>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -7043,93 +6612,65 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14534
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">305
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7797
-</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1274
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17227
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
-</t>
+          <t>061</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">936
+          <t xml:space="preserve">2936
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1138
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1649
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">510
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>4942</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
+          <t xml:space="preserve">1918
+</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">781
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3414
@@ -7138,36 +6679,22 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16680
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="n"/>
+      <c r="W45" s="3" t="n"/>
+      <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32423
+          <t xml:space="preserve">9923
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
+          <t xml:space="preserve">1985
 </t>
         </is>
       </c>
@@ -7198,8 +6725,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -7208,65 +6734,62 @@
 </t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">101
 </t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">187
 </t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">684
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">1984
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">293
 </t>
@@ -7274,54 +6797,54 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -764,7 +764,7 @@
 </t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
@@ -772,37 +772,37 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">227
 </t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">764
 </t>
         </is>
       </c>
@@ -812,9 +812,9 @@
 </t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">017
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -824,31 +824,31 @@
 </t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12811
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
-</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
+          <t xml:space="preserve">561
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -860,7 +860,7 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="8" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
@@ -868,16 +868,11 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1743
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17543
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -899,7 +894,8 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -908,7 +904,7 @@
 </t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -928,13 +924,13 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -944,13 +940,13 @@
 </t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
@@ -958,22 +954,23 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="8" t="inlineStr">
+          <t xml:space="preserve">0 4
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -985,7 +982,7 @@
 </t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
@@ -993,17 +990,17 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
@@ -1023,7 +1020,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -1048,13 +1045,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123680
+          <t xml:space="preserve">2681
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -1066,13 +1063,13 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2063
-</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4103
+          <t xml:space="preserve">635
+</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1084,30 +1081,35 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">251
 </t>
@@ -1115,23 +1117,23 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -1139,7 +1141,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1150,7 +1153,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -1160,13 +1163,13 @@
 </t>
         </is>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="X6" s="8" t="inlineStr">
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -1174,13 +1177,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">454
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1215,9 +1218,9 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -1227,26 +1230,27 @@
 </t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>9444</t>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0113
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">011
 </t>
         </is>
       </c>
@@ -1264,28 +1268,29 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19808
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119
-</t>
-        </is>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
+          <t xml:space="preserve">319
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">253
 </t>
@@ -1299,13 +1304,13 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -1315,7 +1320,7 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -1354,101 +1359,101 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193680
+          <t xml:space="preserve">96811
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">335
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">333
 </t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">417
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1965
-</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">019
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333
-</t>
-        </is>
-      </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">279
 </t>
@@ -1456,11 +1461,11 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
+          <t xml:space="preserve">948
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
@@ -1478,7 +1483,7 @@
 </t>
         </is>
       </c>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
@@ -1511,24 +1516,49 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171836
-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
+          <t xml:space="preserve">11850
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1617
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1074
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13549
+</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121008
+</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -1538,9 +1568,24 @@
 </t>
         </is>
       </c>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1094
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11080
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4870
@@ -1553,37 +1598,57 @@
 </t>
         </is>
       </c>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3" t="n"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1566
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1244
+</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13715
+          <t xml:space="preserve">1537905
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9080
+          <t xml:space="preserve">3080
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901
-</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 2 20
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14200
+</t>
+        </is>
+      </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10325
+          <t xml:space="preserve">11395
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13891
+          <t xml:space="preserve">5891
 </t>
         </is>
       </c>
@@ -1608,13 +1673,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23567
-</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">3567
+</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
@@ -1624,7 +1689,7 @@
 </t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">269
 </t>
@@ -1636,25 +1701,25 @@
 </t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">42
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -1675,7 +1740,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -1685,19 +1750,19 @@
 </t>
         </is>
       </c>
-      <c r="Q10" s="8" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="R10" s="8" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">275
 </t>
@@ -1709,7 +1774,7 @@
 </t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -1721,7 +1786,7 @@
 </t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr">
+      <c r="W10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
@@ -1735,7 +1800,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">14178
 </t>
         </is>
       </c>
@@ -1760,22 +1825,23 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t xml:space="preserve">420
+</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">933
+          <t xml:space="preserve">353
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
@@ -1783,13 +1849,13 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
@@ -1799,21 +1865,21 @@
 </t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">711
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">0104
+</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -1831,13 +1897,13 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -1853,7 +1919,7 @@
 </t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">285
 </t>
@@ -1865,21 +1931,21 @@
 </t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
+      <c r="V11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">295
 </t>
         </is>
       </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6551
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -1891,7 +1957,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -1916,94 +1982,94 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418240
+          <t xml:space="preserve">12182
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">328
 </t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2203
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -2018,17 +2084,17 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19580
-</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr">
+      <c r="V12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">296
 </t>
@@ -2048,13 +2114,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7132
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
@@ -2073,13 +2139,13 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12301
-</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2291
+          <t xml:space="preserve">2301
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -2089,7 +2155,7 @@
 </t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -2101,7 +2167,7 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -2113,31 +2179,31 @@
 </t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -2145,24 +2211,29 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2291
-</t>
-        </is>
-      </c>
-      <c r="R13" s="8" t="inlineStr">
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
         </is>
       </c>
-      <c r="S13" s="8" t="inlineStr">
+      <c r="S13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">273
 </t>
@@ -2170,17 +2241,17 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
-</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
+          <t xml:space="preserve">679
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
         </is>
       </c>
-      <c r="V13" s="8" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
@@ -2200,13 +2271,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">8008
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -2225,7 +2296,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18214
+          <t xml:space="preserve">8214
 </t>
         </is>
       </c>
@@ -2235,9 +2306,9 @@
 </t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0195
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2247,38 +2318,39 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">801
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2288,7 +2360,7 @@
 </t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -2296,25 +2368,25 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
+          <t xml:space="preserve">0 4
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">273
 </t>
         </is>
       </c>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2332,7 +2404,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -2348,7 +2420,7 @@
 </t>
         </is>
       </c>
-      <c r="X14" s="8" t="inlineStr">
+      <c r="X14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -2356,13 +2428,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2385,7 +2457,7 @@
 </t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">314
 </t>
@@ -2393,19 +2465,19 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -2417,18 +2489,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0080
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2438,13 +2511,13 @@
 </t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">224
 </t>
@@ -2452,7 +2525,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -2462,7 +2535,7 @@
 </t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">300
 </t>
@@ -2474,7 +2547,7 @@
 </t>
         </is>
       </c>
-      <c r="S15" s="8" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">300
 </t>
@@ -2486,25 +2559,25 @@
 </t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">250
 </t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
+      <c r="W15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="X15" s="8" t="inlineStr">
+      <c r="X15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -2512,14 +2585,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">7166
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2535,12 +2607,21 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153081
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15242
+</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2551,19 +2632,19 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1545
+          <t xml:space="preserve">5245
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -2575,22 +2656,37 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">1624
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11290
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14900
+          <t xml:space="preserve">4900
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2600,32 +2696,57 @@
 </t>
         </is>
       </c>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1257
+</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1427
+</t>
+        </is>
+      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13310
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763
-</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4126
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2512
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1400
+</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13861
+          <t xml:space="preserve">138611
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">423
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2662,11 +2783,11 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">109
 </t>
@@ -2680,7 +2801,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2690,7 +2811,12 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="n"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">206
@@ -2703,10 +2829,9 @@
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>8886</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2717,23 +2842,23 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">285
 </t>
@@ -2745,20 +2870,25 @@
 </t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">153
 </t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
+      <c r="V17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">273
 </t>
         </is>
       </c>
-      <c r="W17" s="3" t="n"/>
-      <c r="X17" s="3" t="inlineStr">
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
@@ -2766,13 +2896,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17172
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2791,101 +2921,98 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
-</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1714
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">697
+</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">322
 </t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">672
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0084
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
-</t>
-        </is>
-      </c>
-      <c r="R18" s="8" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">253
 </t>
         </is>
       </c>
-      <c r="S18" s="8" t="inlineStr">
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">278
 </t>
@@ -2897,13 +3024,13 @@
 </t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">011
-</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">283
 </t>
@@ -2917,19 +3044,19 @@
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1776
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2948,17 +3075,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13262
+          <t xml:space="preserve">3262
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
 </t>
@@ -2976,7 +3103,7 @@
 </t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -2990,37 +3117,37 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
 </t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -3038,11 +3165,11 @@
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="S19" s="8" t="inlineStr">
+          <t xml:space="preserve">553
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
@@ -3050,11 +3177,11 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
+          <t xml:space="preserve">605
+</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
@@ -3072,7 +3199,7 @@
 </t>
         </is>
       </c>
-      <c r="X19" s="8" t="inlineStr">
+      <c r="X19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">292
 </t>
@@ -3080,7 +3207,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -3105,18 +3232,19 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12990
+          <t xml:space="preserve">28990
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3134,25 +3262,25 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3162,7 +3290,7 @@
 </t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">197
 </t>
@@ -3170,26 +3298,31 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">279
 </t>
         </is>
       </c>
-      <c r="R20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2384
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3201,7 +3334,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
@@ -3223,7 +3356,7 @@
 </t>
         </is>
       </c>
-      <c r="X20" s="8" t="inlineStr">
+      <c r="X20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">263
 </t>
@@ -3231,7 +3364,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -3256,7 +3389,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13575
+          <t xml:space="preserve">3575
 </t>
         </is>
       </c>
@@ -3268,37 +3401,43 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8281
+</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3310,35 +3449,35 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10010
-</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">010
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 0
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">301
 </t>
         </is>
       </c>
-      <c r="R21" s="8" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -3352,7 +3491,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
@@ -3368,7 +3507,7 @@
 </t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
+      <c r="W21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -3382,13 +3521,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">184841
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
@@ -3407,28 +3546,29 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12949
+          <t xml:space="preserve">9929
 </t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -3436,26 +3576,31 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -3473,17 +3618,17 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">000
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
+          <t xml:space="preserve">108000
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">310
 </t>
@@ -3503,7 +3648,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
@@ -3513,21 +3658,21 @@
 </t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
+      <c r="V22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
+      <c r="W22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2165
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3556,20 +3701,39 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16101
+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1554
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3584,45 +3748,90 @@
 </t>
         </is>
       </c>
-      <c r="K23" s="3" t="n"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 78
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16133
+</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4940
 </t>
         </is>
       </c>
-      <c r="P23" s="3" t="n"/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12529
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="n"/>
-      <c r="S23" s="3" t="n"/>
+          <t xml:space="preserve">1529
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12406
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1153947
+</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13200
+          <t xml:space="preserve">3200
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1796
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
+          <t xml:space="preserve">796 1
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1406
+</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4220
@@ -3631,7 +3840,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -3650,8 +3859,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -3662,7 +3870,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">092
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3686,15 +3894,20 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">019
+</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3706,33 +3919,35 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">227
+</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">053
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="R24" s="8" t="inlineStr">
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S24" s="8" t="inlineStr">
+      <c r="S24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">279
 </t>
@@ -3740,7 +3955,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
@@ -3756,13 +3971,13 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
+      <c r="W24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="X24" s="8" t="inlineStr">
+      <c r="X24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">281
 </t>
@@ -3770,14 +3985,13 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">553
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3795,7 +4009,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
@@ -3813,22 +4027,28 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="I25" s="3" t="n"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">23
@@ -3837,7 +4057,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3849,10 +4069,11 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1944</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">229
 </t>
@@ -3860,13 +4081,13 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3882,7 +4103,7 @@
 </t>
         </is>
       </c>
-      <c r="S25" s="8" t="inlineStr">
+      <c r="S25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">261
 </t>
@@ -3896,23 +4117,23 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
+      <c r="W25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
         </is>
       </c>
-      <c r="X25" s="8" t="inlineStr">
+      <c r="X25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -3920,13 +4141,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">9 52
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3945,11 +4166,11 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23450
-</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
+          <t xml:space="preserve">8450
+</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">317
 </t>
@@ -3957,10 +4178,11 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>6151</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">261
 </t>
@@ -3974,11 +4196,16 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n"/>
+          <t xml:space="preserve">8868
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
@@ -3987,7 +4214,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4011,7 +4238,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -4021,13 +4248,13 @@
 </t>
         </is>
       </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="R26" s="8" t="inlineStr">
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -4035,7 +4262,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4051,13 +4278,13 @@
 </t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">272
 </t>
         </is>
       </c>
-      <c r="W26" s="8" t="inlineStr">
+      <c r="W26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">236
 </t>
@@ -4065,12 +4292,13 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>621</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1743
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -4095,7 +4323,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24182
+          <t xml:space="preserve">14182
 </t>
         </is>
       </c>
@@ -4107,36 +4335,43 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">861
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">387
+</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="n"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t xml:space="preserve">52
+</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4152,7 +4387,7 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -4160,13 +4395,13 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">042
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -4176,13 +4411,13 @@
 </t>
         </is>
       </c>
-      <c r="R27" s="8" t="inlineStr">
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S27" s="8" t="inlineStr">
+      <c r="S27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
@@ -4190,7 +4425,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
@@ -4208,11 +4443,11 @@
       </c>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
-</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">302
 </t>
@@ -4220,13 +4455,13 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1742
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -4257,7 +4492,8 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4274,13 +4510,13 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4292,7 +4528,8 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t xml:space="preserve">800
+</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4303,18 +4540,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -4326,7 +4564,7 @@
       </c>
       <c r="Q28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">9798
 </t>
         </is>
       </c>
@@ -4336,7 +4574,7 @@
 </t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
+      <c r="S28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">289
 </t>
@@ -4344,23 +4582,23 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2244
-</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -4368,7 +4606,7 @@
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2603
+          <t xml:space="preserve">6595
 </t>
         </is>
       </c>
@@ -4380,8 +4618,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4399,7 +4636,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">1221121
 </t>
         </is>
       </c>
@@ -4417,7 +4654,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
@@ -4435,7 +4672,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4445,25 +4682,20 @@
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
+      <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241 9
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">254
 </t>
@@ -4471,16 +4703,17 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Q29" s="8" t="inlineStr">
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -4500,23 +4733,23 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350
-</t>
-        </is>
-      </c>
-      <c r="W29" s="8" t="inlineStr">
+          <t xml:space="preserve">737
+</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">515
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -4530,13 +4763,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4553,31 +4786,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6251
+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">565
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11200
+</t>
+        </is>
+      </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069
+          <t xml:space="preserve">5698
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
@@ -4587,42 +4840,87 @@
 </t>
         </is>
       </c>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1802
+</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14895
+          <t xml:space="preserve">4895
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="n"/>
-      <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3121
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01 35
+</t>
+        </is>
+      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13445
+          <t xml:space="preserve">3445
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="n"/>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="n"/>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1274
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1153
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14115
+          <t xml:space="preserve">4115
 </t>
         </is>
       </c>
@@ -4651,9 +4949,9 @@
 </t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">313
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12461
 </t>
         </is>
       </c>
@@ -4665,25 +4963,25 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">956
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4694,19 +4992,19 @@
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="M31" s="8" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">236
 </t>
@@ -4714,29 +5012,29 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1979
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
         </is>
       </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">042
-</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">271
 </t>
@@ -4744,41 +5042,43 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t>2551</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t xml:space="preserve">1823
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16828
 </t>
         </is>
       </c>
@@ -4797,11 +5097,11 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12635
-</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
+          <t xml:space="preserve">2635
+</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -4813,7 +5113,7 @@
 </t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -4833,11 +5133,16 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">34
@@ -4850,13 +5155,13 @@
 </t>
         </is>
       </c>
-      <c r="M32" s="8" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr">
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -4864,7 +5169,8 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t xml:space="preserve">990
+</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4879,13 +5185,13 @@
 </t>
         </is>
       </c>
-      <c r="R32" s="8" t="inlineStr">
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="S32" s="8" t="inlineStr">
+      <c r="S32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">279
 </t>
@@ -4893,7 +5199,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
@@ -4903,33 +5209,33 @@
 </t>
         </is>
       </c>
-      <c r="V32" s="8" t="inlineStr">
+      <c r="V32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">271
 </t>
         </is>
       </c>
-      <c r="W32" s="8" t="inlineStr">
+      <c r="W32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="X32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4948,7 +5254,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -4972,13 +5278,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4988,10 +5294,14 @@
 </t>
         </is>
       </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -5007,7 +5317,7 @@
 </t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -5019,7 +5329,12 @@
 </t>
         </is>
       </c>
-      <c r="P33" s="3" t="n"/>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
@@ -5032,7 +5347,7 @@
 </t>
         </is>
       </c>
-      <c r="S33" s="8" t="inlineStr">
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
@@ -5040,29 +5355,29 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="W33" s="8" t="inlineStr">
+      <c r="W33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="X33" s="8" t="inlineStr">
+      <c r="X33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -5070,13 +5385,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -5095,7 +5410,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11178
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -5105,7 +5420,7 @@
 </t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">191
 </t>
@@ -5113,7 +5428,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">24 9
 </t>
         </is>
       </c>
@@ -5125,7 +5440,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1678
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -5162,23 +5477,23 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="8" t="inlineStr">
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">301
 </t>
         </is>
       </c>
-      <c r="R34" s="8" t="inlineStr">
+      <c r="R34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -5192,23 +5507,23 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
+          <t xml:space="preserve">802
+</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">263
 </t>
         </is>
       </c>
-      <c r="W34" s="8" t="inlineStr">
+      <c r="W34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
@@ -5222,13 +5537,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5247,23 +5562,23 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12844
-</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">095
-</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
+          <t xml:space="preserve">2844
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -5283,12 +5598,13 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5300,19 +5616,25 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>2431</t>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -5328,13 +5650,13 @@
 </t>
         </is>
       </c>
-      <c r="R35" s="8" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="S35" s="8" t="inlineStr">
+      <c r="S35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -5342,7 +5664,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2754
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
@@ -5364,9 +5686,9 @@
 </t>
         </is>
       </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
+      <c r="X35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29593
 </t>
         </is>
       </c>
@@ -5378,7 +5700,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
@@ -5421,13 +5743,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5445,7 +5767,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -5461,7 +5783,7 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -5469,13 +5791,13 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -5499,29 +5821,29 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="W36" s="8" t="inlineStr">
+      <c r="W36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="X36" s="8" t="inlineStr">
+      <c r="X36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -5535,7 +5857,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -5558,12 +5880,27 @@
 </t>
         </is>
       </c>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1429
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11215
+</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
@@ -5575,11 +5912,16 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="n"/>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1179
@@ -5592,23 +5934,48 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3" t="n"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="n"/>
-      <c r="S37" s="3" t="n"/>
+          <t xml:space="preserve">2331
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1363
+</t>
+        </is>
+      </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3936
@@ -5617,16 +5984,31 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="n"/>
-      <c r="W37" s="3" t="n"/>
-      <c r="X37" s="3" t="n"/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1298
+</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14160
+          <t xml:space="preserve">124660
 </t>
         </is>
       </c>
@@ -5651,7 +6033,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1633
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
@@ -5663,7 +6045,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2 0 0
 </t>
         </is>
       </c>
@@ -5679,20 +6061,30 @@
 </t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">686
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 1
+</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5701,7 +6093,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5713,7 +6105,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5723,7 +6115,7 @@
 </t>
         </is>
       </c>
-      <c r="Q38" s="8" t="inlineStr">
+      <c r="Q38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
@@ -5735,31 +6127,31 @@
 </t>
         </is>
       </c>
-      <c r="S38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9273
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8111
-</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W38" s="8" t="inlineStr">
+          <t xml:space="preserve">8287
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">225
 </t>
@@ -5773,7 +6165,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18392
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
@@ -5798,19 +6190,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
-</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">907
-</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">693
+          <t xml:space="preserve">3320
+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5828,7 +6220,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5840,13 +6232,13 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5870,19 +6262,19 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -5900,7 +6292,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">66853
 </t>
         </is>
       </c>
@@ -5910,9 +6302,9 @@
 </t>
         </is>
       </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 78
 </t>
         </is>
       </c>
@@ -5924,7 +6316,7 @@
       </c>
       <c r="X39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -5936,7 +6328,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1061
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -5955,7 +6347,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">2788
 </t>
         </is>
       </c>
@@ -5971,21 +6363,21 @@
 </t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2297
-</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">102
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -5997,13 +6389,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6015,10 +6407,11 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -6032,19 +6425,19 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">307
-</t>
-        </is>
-      </c>
-      <c r="R40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">807
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -6056,17 +6449,17 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
+          <t xml:space="preserve">654
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
@@ -6078,7 +6471,7 @@
 </t>
         </is>
       </c>
-      <c r="X40" s="8" t="inlineStr">
+      <c r="X40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">273
 </t>
@@ -6092,7 +6485,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">18114
 </t>
         </is>
       </c>
@@ -6111,7 +6504,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">2486
 </t>
         </is>
       </c>
@@ -6121,7 +6514,7 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
@@ -6135,7 +6528,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6145,9 +6538,9 @@
 </t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -6159,11 +6552,11 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -6171,7 +6564,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -6183,7 +6576,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1938
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -6195,7 +6588,7 @@
       </c>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">093
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -6205,7 +6598,7 @@
 </t>
         </is>
       </c>
-      <c r="S41" s="8" t="inlineStr">
+      <c r="S41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">287
 </t>
@@ -6213,17 +6606,17 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205
-</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
+          <t xml:space="preserve">805
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="V41" s="8" t="inlineStr">
+      <c r="V41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">271
 </t>
@@ -6231,10 +6624,11 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>6451</t>
-        </is>
-      </c>
-      <c r="X41" s="8" t="inlineStr">
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
@@ -6242,16 +6636,11 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18411
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1811
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6297,25 +6686,25 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6325,9 +6714,9 @@
 </t>
         </is>
       </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -6339,29 +6728,29 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="8" t="inlineStr">
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">309
 </t>
         </is>
       </c>
-      <c r="R42" s="8" t="inlineStr">
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S42" s="8" t="inlineStr">
+      <c r="S42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">276
 </t>
@@ -6369,19 +6758,19 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
-</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2071
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -6393,7 +6782,7 @@
       </c>
       <c r="X42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393
+          <t xml:space="preserve">89535
 </t>
         </is>
       </c>
@@ -6424,7 +6813,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23116
+          <t xml:space="preserve">3126
 </t>
         </is>
       </c>
@@ -6434,7 +6823,7 @@
 </t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
@@ -6458,7 +6847,12 @@
 </t>
         </is>
       </c>
-      <c r="I43" s="3" t="n"/>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">416
+</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -6477,13 +6871,13 @@
 </t>
         </is>
       </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -6491,29 +6885,29 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="8" t="inlineStr">
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="R43" s="8" t="inlineStr">
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
         </is>
       </c>
-      <c r="S43" s="8" t="inlineStr">
+      <c r="S43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
@@ -6521,7 +6915,7 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -6533,7 +6927,7 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -6545,18 +6939,18 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>958</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1843
+          <t xml:space="preserve">18495
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -6573,7 +6967,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -6612,27 +7011,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17227
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+          <t xml:space="preserve">14234
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9227
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101011
+</t>
+        </is>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>061</t>
+          <t xml:space="preserve">121010
+</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2936
+          <t xml:space="preserve">936
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">025
 </t>
         </is>
       </c>
@@ -6644,33 +7058,53 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1009001604
+</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161285
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">49160
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
+          <t xml:space="preserve">12463
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3414
@@ -6679,22 +7113,36 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16680
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
+          <t xml:space="preserve">66 8
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2220
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14124
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1225
+</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923
-</t>
+          <t>39831</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">108209
 </t>
         </is>
       </c>
@@ -6717,7 +7165,7 @@
 </t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">305
 </t>
@@ -6725,7 +7173,8 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -6734,7 +7183,7 @@
 </t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">101
 </t>
@@ -6742,109 +7191,115 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 5
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="S46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>6451</t>
-        </is>
-      </c>
-      <c r="S46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2922
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -800,9 +800,9 @@
 </t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">764
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -814,8 +814,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>061</t>
         </is>
       </c>
       <c r="Q4" s="8" t="inlineStr">
@@ -830,7 +829,7 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">281
 </t>
@@ -860,15 +859,15 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
+      <c r="X4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17543
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -924,13 +923,13 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -946,9 +945,9 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -990,7 +989,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -1012,7 +1011,7 @@
 </t>
         </is>
       </c>
-      <c r="X5" s="8" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -1045,13 +1044,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -1061,15 +1060,15 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">635
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -1087,7 +1086,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1117,7 +1116,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9720
 </t>
         </is>
       </c>
@@ -1127,9 +1126,9 @@
 </t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -1153,7 +1152,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1177,13 +1176,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">454
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1202,7 +1201,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">82182
 </t>
         </is>
       </c>
@@ -1220,7 +1219,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -1232,25 +1231,25 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -1308,9 +1307,9 @@
 </t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -1359,13 +1358,13 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96811
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
@@ -1383,7 +1382,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1395,7 +1394,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1407,7 +1406,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1431,7 +1430,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
@@ -1461,7 +1460,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
@@ -1497,7 +1496,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1516,7 +1515,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11850
+          <t xml:space="preserve">17830
 </t>
         </is>
       </c>
@@ -1534,7 +1533,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13549
+          <t xml:space="preserve">1345
 </t>
         </is>
       </c>
@@ -1546,7 +1545,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121008
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
@@ -1576,13 +1575,13 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11080
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1600,7 +1599,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">85566
 </t>
         </is>
       </c>
@@ -1612,7 +1611,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537905
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
@@ -1630,25 +1629,25 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 2 20
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11395
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891
+          <t xml:space="preserve">3891
 </t>
         </is>
       </c>
@@ -1673,13 +1672,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
-</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2567
+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1703,26 +1702,31 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">42
 </t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1770,7 +1774,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">6 1 6
 </t>
         </is>
       </c>
@@ -1786,13 +1790,13 @@
 </t>
         </is>
       </c>
-      <c r="W10" s="8" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
         </is>
       </c>
-      <c r="X10" s="8" t="inlineStr">
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">279
 </t>
@@ -1800,7 +1804,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14178
+          <t xml:space="preserve">8778
 </t>
         </is>
       </c>
@@ -1829,15 +1833,15 @@
 </t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">353
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333
+</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
@@ -1849,37 +1853,37 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0104
-</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1927,7 +1931,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1563
+          <t xml:space="preserve">2563
 </t>
         </is>
       </c>
@@ -1963,7 +1967,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -1988,7 +1992,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -2018,13 +2022,13 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2048,7 +2052,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2072,7 +2076,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25 8
 </t>
         </is>
       </c>
@@ -2084,7 +2088,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -2106,7 +2110,7 @@
 </t>
         </is>
       </c>
-      <c r="X12" s="8" t="inlineStr">
+      <c r="X12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">303
 </t>
@@ -2114,13 +2118,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">7132
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2139,7 +2143,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">2381
 </t>
         </is>
       </c>
@@ -2175,7 +2179,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2217,7 +2221,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2263,7 +2267,7 @@
 </t>
         </is>
       </c>
-      <c r="X13" s="8" t="inlineStr">
+      <c r="X13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">278
 </t>
@@ -2271,7 +2275,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8008
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -2296,7 +2300,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8214
+          <t xml:space="preserve">12214
 </t>
         </is>
       </c>
@@ -2344,7 +2348,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2428,13 +2432,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -2465,52 +2469,52 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -2535,7 +2539,7 @@
 </t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">300
 </t>
@@ -2559,13 +2563,13 @@
 </t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">250
 </t>
@@ -2585,7 +2589,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7166
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
@@ -2615,7 +2619,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15242
+          <t xml:space="preserve">1542
 </t>
         </is>
       </c>
@@ -2626,25 +2630,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2656,25 +2659,25 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1624
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -2698,13 +2701,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2716,19 +2719,19 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2512
+          <t xml:space="preserve">2120
 </t>
         </is>
       </c>
@@ -2740,13 +2743,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138611
+          <t xml:space="preserve">3861
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -2771,8 +2774,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2783,7 +2785,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2813,7 +2815,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -2829,24 +2831,24 @@
 </t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>8886</t>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">305
 </t>
@@ -2866,11 +2868,11 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+          <t xml:space="preserve">19662
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">153
 </t>
@@ -2888,7 +2890,7 @@
 </t>
         </is>
       </c>
-      <c r="X17" s="8" t="inlineStr">
+      <c r="X17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
@@ -2896,7 +2898,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">7722
 </t>
         </is>
       </c>
@@ -2926,10 +2928,10 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
+          <t>324</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
@@ -2947,15 +2949,15 @@
 </t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1714
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2972,13 +2974,13 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">697
-</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -3020,7 +3022,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -3042,7 +3044,7 @@
 </t>
         </is>
       </c>
-      <c r="X18" s="8" t="inlineStr">
+      <c r="X18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">298
 </t>
@@ -3056,8 +3058,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3103,7 +3104,7 @@
 </t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -3141,7 +3142,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -3157,15 +3158,15 @@
 </t>
         </is>
       </c>
-      <c r="Q19" s="8" t="inlineStr">
+      <c r="Q19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">317
 </t>
         </is>
       </c>
-      <c r="R19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">553
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -3181,19 +3182,19 @@
 </t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="U19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
+      <c r="V19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">257
 </t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
+      <c r="W19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -3232,7 +3233,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28990
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
@@ -3248,7 +3249,7 @@
 </t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -3262,7 +3263,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3344,13 +3345,13 @@
 </t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
+      <c r="V20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">250
 </t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
+      <c r="W20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
@@ -3401,7 +3402,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3411,13 +3412,13 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8281
-</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
@@ -3425,13 +3426,13 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3461,13 +3462,13 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">8000
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 0
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3513,7 +3514,7 @@
 </t>
         </is>
       </c>
-      <c r="X21" s="8" t="inlineStr">
+      <c r="X21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">288
 </t>
@@ -3521,13 +3522,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184841
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3546,13 +3547,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9929
-</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
+          <t>14929</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -3568,7 +3568,7 @@
 </t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3600,16 +3600,16 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
@@ -3618,19 +3618,19 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
@@ -3715,25 +3715,25 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">2258
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -3762,13 +3762,13 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 78
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16133
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3792,13 +3792,13 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12406
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153947
+          <t xml:space="preserve">11397
 </t>
         </is>
       </c>
@@ -3810,26 +3810,25 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796 1
+          <t xml:space="preserve">795 1
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3840,7 +3839,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3859,10 +3858,10 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
+          <t>3803</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">311
 </t>
@@ -3894,24 +3893,24 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">019
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">197
 </t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -3931,67 +3930,68 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">844
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">053
 </t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">640
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4045,8 +4045,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -4061,16 +4060,14 @@
 </t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>1104</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -4127,7 +4124,7 @@
 </t>
         </is>
       </c>
-      <c r="W25" s="3" t="inlineStr">
+      <c r="W25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
@@ -4166,11 +4163,11 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8450
-</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+          <t xml:space="preserve">23450
+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">317
 </t>
@@ -4196,13 +4193,13 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8868
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4214,7 +4211,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4232,8 +4229,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -4242,15 +4238,10 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">854
+      <c r="P26" s="3" t="n"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
@@ -4323,11 +4314,11 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14182
-</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
+          <t xml:space="preserve">4182
+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">329
 </t>
@@ -4345,9 +4336,9 @@
 </t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">387
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4359,7 +4350,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -4387,7 +4378,7 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -4441,15 +4432,14 @@
 </t>
         </is>
       </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>6551</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">082
 </t>
         </is>
       </c>
@@ -4486,7 +4476,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -4510,7 +4500,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -4528,7 +4518,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4562,9 +4552,9 @@
 </t>
         </is>
       </c>
-      <c r="Q28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9798
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -4588,7 +4578,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -4604,15 +4594,15 @@
 </t>
         </is>
       </c>
-      <c r="X28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6595
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
@@ -4636,8 +4626,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221121
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4652,9 +4641,9 @@
 </t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">472
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -4678,20 +4667,20 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241 9
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4719,7 +4708,7 @@
 </t>
         </is>
       </c>
-      <c r="R29" s="8" t="inlineStr">
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -4739,7 +4728,7 @@
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">515
+          <t xml:space="preserve">073
 </t>
         </is>
       </c>
@@ -4755,7 +4744,7 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="8" t="inlineStr">
+      <c r="X29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -4763,13 +4752,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4786,21 +4775,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6251
-</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
-</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4812,49 +4795,48 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9228
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
@@ -4866,25 +4848,25 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">755
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01 35
+          <t xml:space="preserve">18 35
 </t>
         </is>
       </c>
@@ -4949,9 +4931,9 @@
 </t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12461
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">513
 </t>
         </is>
       </c>
@@ -4963,17 +4945,12 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
@@ -5000,7 +4977,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">20 2
 </t>
         </is>
       </c>
@@ -5046,13 +5023,13 @@
 </t>
         </is>
       </c>
-      <c r="U31" s="3" t="inlineStr">
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
+      <c r="V31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
@@ -5060,7 +5037,7 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -5072,13 +5049,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16828
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5125,7 +5102,7 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
@@ -5139,7 +5116,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5223,19 +5200,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -5254,7 +5231,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
@@ -5264,59 +5241,60 @@
 </t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">006
+</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">206
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
@@ -5355,7 +5333,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
@@ -5391,7 +5369,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5420,7 +5398,7 @@
 </t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
 </t>
@@ -5450,7 +5428,11 @@
 </t>
         </is>
       </c>
-      <c r="J34" s="3" t="n"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">59
@@ -5483,7 +5465,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5507,13 +5489,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">702
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5523,7 +5505,7 @@
 </t>
         </is>
       </c>
-      <c r="W34" s="3" t="inlineStr">
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
@@ -5537,13 +5519,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5614,7 +5596,7 @@
 </t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
@@ -5628,7 +5610,7 @@
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5664,7 +5646,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5688,7 +5670,7 @@
       </c>
       <c r="X35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">29593
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -5700,7 +5682,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5719,7 +5701,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -5743,7 +5725,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5761,7 +5743,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5797,7 +5779,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -5825,12 +5807,7 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+      <c r="U36" s="3" t="n"/>
       <c r="V36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -5839,8 +5816,7 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -5857,7 +5833,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5888,13 +5864,13 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
@@ -5918,103 +5894,103 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18079
+</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0229
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1338
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39236
+</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1179
-</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1034
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2331
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1272
-</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1363
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3936
-</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1298
-</t>
-        </is>
-      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124660
+          <t xml:space="preserve">4160
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6033,7 +6009,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
+          <t xml:space="preserve">1653
 </t>
         </is>
       </c>
@@ -6063,7 +6039,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18 6
 </t>
         </is>
       </c>
@@ -6073,15 +6049,15 @@
 </t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 8
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6093,7 +6069,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6115,9 +6091,9 @@
 </t>
         </is>
       </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
@@ -6129,13 +6105,12 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>485</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8287
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
@@ -6147,7 +6122,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -6157,7 +6132,7 @@
 </t>
         </is>
       </c>
-      <c r="X38" s="8" t="inlineStr">
+      <c r="X38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -6165,7 +6140,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
@@ -6190,7 +6165,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -6218,7 +6193,7 @@
 </t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -6226,13 +6201,13 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -6268,7 +6243,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
@@ -6292,7 +6267,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66853
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
@@ -6314,9 +6289,9 @@
 </t>
         </is>
       </c>
-      <c r="X39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -6347,11 +6322,11 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2788
-</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
+          <t xml:space="preserve">27281
+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">308
 </t>
@@ -6375,9 +6350,9 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -6389,7 +6364,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -6411,9 +6386,9 @@
 </t>
         </is>
       </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -6431,13 +6406,13 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6455,7 +6430,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -6485,7 +6460,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18114
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6504,7 +6479,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2486
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6552,7 +6527,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6586,13 +6561,13 @@
 </t>
         </is>
       </c>
-      <c r="Q41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">953
-</t>
-        </is>
-      </c>
-      <c r="R41" s="8" t="inlineStr">
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -6606,7 +6581,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6636,11 +6611,16 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n"/>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6684,9 +6664,9 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -6698,7 +6678,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6714,9 +6694,9 @@
 </t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -6734,7 +6714,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -6780,15 +6760,15 @@
 </t>
         </is>
       </c>
-      <c r="X42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89535
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -6813,17 +6793,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126
-</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
+          <t xml:space="preserve">3116
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">307
 </t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
@@ -6831,8 +6811,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -6841,15 +6820,15 @@
 </t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">416
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6891,7 +6870,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6939,12 +6918,12 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>854</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18495
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
@@ -7017,24 +6996,25 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>705</t>
+          <t xml:space="preserve">1027
+</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101011
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121010
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
@@ -7046,57 +7026,56 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">025
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">18149
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009001604
+          <t xml:space="preserve">1050816
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161285
+          <t xml:space="preserve">18205
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49160
+          <t xml:space="preserve">4918
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">16 9
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12463
+          <t xml:space="preserve">8463
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>633</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -7119,30 +7098,31 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14124
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t xml:space="preserve">99295
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108209
+          <t xml:space="preserve">0805
 </t>
         </is>
       </c>
@@ -7165,7 +7145,7 @@
 </t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">305
 </t>
@@ -7183,15 +7163,15 @@
 </t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">091
 </t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
@@ -7209,7 +7189,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 5
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7221,7 +7201,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -7243,9 +7223,9 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -7255,9 +7235,9 @@
 </t>
         </is>
       </c>
-      <c r="S46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -7267,39 +7247,39 @@
 </t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">738
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
@@ -743,7 +743,8 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>336</t>
+          <t xml:space="preserve">335
+</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -778,7 +779,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -802,7 +803,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -814,10 +815,11 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>061</t>
-        </is>
-      </c>
-      <c r="Q4" s="8" t="inlineStr">
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">330
 </t>
@@ -829,7 +831,7 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">281
 </t>
@@ -859,9 +861,9 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">921
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -871,7 +873,12 @@
 </t>
         </is>
       </c>
-      <c r="Z4" s="3" t="n"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -945,9 +952,9 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -965,7 +972,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 4
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -989,13 +996,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -1019,13 +1026,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1920
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1044,7 +1051,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">23680
 </t>
         </is>
       </c>
@@ -1068,7 +1075,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1086,7 +1093,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1116,13 +1123,13 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -1146,7 +1153,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">596
 </t>
         </is>
       </c>
@@ -1182,7 +1189,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1201,7 +1208,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
@@ -1231,7 +1238,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1243,13 +1250,13 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -1265,7 +1272,7 @@
 </t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -1283,7 +1290,7 @@
 </t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">319
 </t>
@@ -1325,7 +1332,7 @@
 </t>
         </is>
       </c>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">288
 </t>
@@ -1358,7 +1365,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">23680
 </t>
         </is>
       </c>
@@ -1368,9 +1375,9 @@
 </t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1394,7 +1401,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1430,13 +1437,13 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -1452,7 +1459,7 @@
 </t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">279
 </t>
@@ -1460,11 +1467,11 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
+          <t xml:space="preserve">548
+</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
@@ -1482,7 +1489,7 @@
 </t>
         </is>
       </c>
-      <c r="X8" s="8" t="inlineStr">
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
@@ -1496,7 +1503,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1515,7 +1522,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17830
+          <t xml:space="preserve">17836
 </t>
         </is>
       </c>
@@ -1539,7 +1546,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">543
 </t>
         </is>
       </c>
@@ -1581,7 +1588,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">12 82
 </t>
         </is>
       </c>
@@ -1593,13 +1600,13 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85566
+          <t xml:space="preserve">2556
 </t>
         </is>
       </c>
@@ -1611,7 +1618,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">1375
 </t>
         </is>
       </c>
@@ -1629,7 +1636,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
@@ -1641,7 +1648,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1395
 </t>
         </is>
       </c>
@@ -1653,7 +1660,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
@@ -1672,19 +1679,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">323
+</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1702,13 +1709,13 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1720,13 +1727,13 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1750,7 +1757,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1774,11 +1781,11 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 1 6
-</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
+          <t xml:space="preserve">616
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -1804,13 +1811,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8778
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1835,17 +1842,16 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">892
-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+          <t>333</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
@@ -1853,31 +1859,31 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1931,7 +1937,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2563
+          <t xml:space="preserve">563
 </t>
         </is>
       </c>
@@ -1961,13 +1967,13 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">704
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1986,7 +1992,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12182
+          <t xml:space="preserve">24182
 </t>
         </is>
       </c>
@@ -2014,7 +2020,7 @@
 </t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -2022,13 +2028,13 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2050,7 +2056,7 @@
 </t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">233
 </t>
@@ -2076,7 +2082,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 8
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2092,7 +2098,7 @@
 </t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
@@ -2110,7 +2116,7 @@
 </t>
         </is>
       </c>
-      <c r="X12" s="3" t="inlineStr">
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">303
 </t>
@@ -2118,7 +2124,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7132
+          <t xml:space="preserve">1732
 </t>
         </is>
       </c>
@@ -2143,7 +2149,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381
+          <t xml:space="preserve">2301
 </t>
         </is>
       </c>
@@ -2179,7 +2185,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -2207,7 +2213,7 @@
 </t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -2221,7 +2227,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2281,7 +2287,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2300,7 +2306,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12214
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
@@ -2310,7 +2316,7 @@
 </t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">195
 </t>
@@ -2330,7 +2336,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2364,7 +2370,7 @@
 </t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -2378,7 +2384,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 4
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2432,13 +2438,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2457,7 +2463,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">23408
 </t>
         </is>
       </c>
@@ -2499,7 +2505,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -2521,7 +2527,7 @@
 </t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">224
 </t>
@@ -2539,7 +2545,7 @@
 </t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">300
 </t>
@@ -2569,15 +2575,15 @@
 </t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">250
 </t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">419
 </t>
         </is>
       </c>
@@ -2595,7 +2601,8 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">74
+</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2613,7 +2620,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153081
+          <t xml:space="preserve">15308
 </t>
         </is>
       </c>
@@ -2625,12 +2632,14 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>992</t>
+          <t xml:space="preserve">997
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">2268
+</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2641,7 +2650,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">11921
 </t>
         </is>
       </c>
@@ -2665,19 +2674,19 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -2701,13 +2710,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1427
 </t>
         </is>
       </c>
@@ -2719,19 +2728,19 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">763
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1365
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -2749,7 +2758,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1423
 </t>
         </is>
       </c>
@@ -2768,13 +2777,14 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
+          <t xml:space="preserve">2306
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2785,7 +2795,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
@@ -2815,7 +2825,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2845,7 +2855,8 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -2868,7 +2879,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19662
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
@@ -2898,13 +2909,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7722
+          <t xml:space="preserve">772
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2923,12 +2934,14 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2937,13 +2950,13 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">257
 </t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
@@ -2951,18 +2964,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2978,13 +2992,13 @@
 </t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
@@ -2998,7 +3012,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -3026,7 +3040,7 @@
 </t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">201
 </t>
@@ -3058,7 +3072,8 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3076,11 +3091,11 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
-</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">322
 </t>
@@ -3140,7 +3155,7 @@
 </t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -3200,7 +3215,7 @@
 </t>
         </is>
       </c>
-      <c r="X19" s="3" t="inlineStr">
+      <c r="X19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">292
 </t>
@@ -3237,7 +3252,7 @@
 </t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">297
 </t>
@@ -3255,7 +3270,7 @@
 </t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">100
 </t>
@@ -3263,7 +3278,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -3285,19 +3300,19 @@
 </t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1197
+</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
@@ -3390,7 +3405,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
@@ -3400,9 +3415,9 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -3418,7 +3433,7 @@
 </t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
@@ -3450,11 +3465,11 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -3462,7 +3477,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000
+          <t xml:space="preserve">16000
 </t>
         </is>
       </c>
@@ -3522,7 +3537,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">18441
 </t>
         </is>
       </c>
@@ -3547,7 +3562,8 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t xml:space="preserve">2949
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3558,13 +3574,13 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2380
 </t>
         </is>
       </c>
@@ -3576,7 +3592,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1674
 </t>
         </is>
       </c>
@@ -3600,7 +3616,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -3610,7 +3626,7 @@
 </t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="N22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">221
 </t>
@@ -3624,13 +3640,13 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3648,13 +3664,13 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -3664,7 +3680,7 @@
 </t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -3678,7 +3694,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -3703,7 +3719,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
@@ -3715,13 +3731,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">0962
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -3733,7 +3749,8 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">882
+</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3768,7 +3785,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
@@ -3798,7 +3815,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -3810,25 +3827,26 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">795 1
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t xml:space="preserve">1406
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3839,7 +3857,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -3858,7 +3876,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t xml:space="preserve">3220
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3867,7 +3886,7 @@
 </t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
@@ -3897,10 +3916,15 @@
 </t>
         </is>
       </c>
-      <c r="J24" s="3" t="n"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3910,7 +3934,7 @@
 </t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -3924,7 +3948,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -3954,7 +3978,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">1640
 </t>
         </is>
       </c>
@@ -3966,7 +3990,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4045,7 +4069,8 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -4060,14 +4085,15 @@
 </t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>1104</t>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>406</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -4124,7 +4150,7 @@
 </t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
+      <c r="W25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
@@ -4138,7 +4164,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 52
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
@@ -4205,7 +4231,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -4229,7 +4255,8 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -4238,10 +4265,15 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="3" t="n"/>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -4253,7 +4285,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -4338,7 +4370,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4350,7 +4382,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -4378,7 +4410,7 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -4434,12 +4466,13 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6551</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">082
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -4470,13 +4503,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2823
+          <t xml:space="preserve">2824
 </t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -4486,9 +4519,9 @@
 </t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
@@ -4498,7 +4531,7 @@
 </t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
@@ -4522,7 +4555,7 @@
 </t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">201
 </t>
@@ -4588,13 +4621,13 @@
 </t>
         </is>
       </c>
-      <c r="W28" s="3" t="inlineStr">
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="X28" s="3" t="inlineStr">
+      <c r="X28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">263
 </t>
@@ -4608,7 +4641,8 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">143
+</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4626,7 +4660,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4671,10 +4705,15 @@
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4708,7 +4747,7 @@
 </t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
+      <c r="R29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -4726,9 +4765,9 @@
 </t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">073
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4758,7 +4797,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4775,10 +4814,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1363
+</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t xml:space="preserve">11565
+</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4789,30 +4834,31 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11200
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t xml:space="preserve">2569
+</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">11718
 </t>
         </is>
       </c>
@@ -4824,19 +4870,19 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -4854,19 +4900,19 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">1455
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4896,13 +4942,13 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1337
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">24115
 </t>
         </is>
       </c>
@@ -4931,9 +4977,9 @@
 </t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">513
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
@@ -4949,7 +4995,12 @@
 </t>
         </is>
       </c>
-      <c r="G31" s="3" t="n"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
@@ -4964,11 +5015,16 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -4977,7 +5033,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 2
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4989,7 +5045,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5025,17 +5081,17 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">231
 </t>
@@ -5055,7 +5111,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5078,7 +5134,7 @@
 </t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -5086,8 +5142,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -5102,7 +5157,7 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
@@ -5116,7 +5171,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5132,7 +5187,7 @@
 </t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -5168,7 +5223,7 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="S32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">279
 </t>
@@ -5194,11 +5249,11 @@
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="X32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
@@ -5206,13 +5261,13 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5231,7 +5286,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
@@ -5241,9 +5296,9 @@
 </t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">006
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -5267,19 +5322,19 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5295,7 +5350,7 @@
 </t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="N33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -5333,7 +5388,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -5367,12 +5422,7 @@
 </t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+      <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -5406,7 +5456,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 9
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -5430,7 +5480,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -5439,7 +5489,7 @@
 </t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">201
 </t>
@@ -5451,7 +5501,7 @@
 </t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr">
+      <c r="N34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">235
 </t>
@@ -5610,7 +5660,7 @@
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -5622,7 +5672,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5670,13 +5720,13 @@
       </c>
       <c r="X35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">093
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">1858
 </t>
         </is>
       </c>
@@ -5701,11 +5751,11 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
+          <t xml:space="preserve">11172
+</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -5725,13 +5775,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5749,7 +5799,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5765,7 +5815,7 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="N36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -5807,7 +5857,12 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="3" t="n"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -5816,7 +5871,8 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>618</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -5827,13 +5883,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5864,19 +5920,19 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">1429
 </t>
         </is>
       </c>
@@ -5894,13 +5950,13 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18079
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5912,49 +5968,49 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0229
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">4950
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 0
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1338
+          <t xml:space="preserve">1331
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1363
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39236
+          <t xml:space="preserve">3936
 </t>
         </is>
       </c>
@@ -5966,19 +6022,19 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
@@ -6009,7 +6065,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6021,13 +6077,13 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 0 0
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6037,9 +6093,9 @@
 </t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18 6
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -6051,13 +6107,13 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 8
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6069,7 +6125,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6091,9 +6147,9 @@
 </t>
         </is>
       </c>
-      <c r="Q38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">566
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -6105,24 +6161,25 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>485</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">788
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -6140,13 +6197,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -6165,7 +6222,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">3323
 </t>
         </is>
       </c>
@@ -6187,7 +6244,7 @@
 </t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">114
 </t>
@@ -6201,52 +6258,52 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">5 8
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">35
 </t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">002
-</t>
-        </is>
-      </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">307
@@ -6267,19 +6324,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 78
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -6289,7 +6346,7 @@
 </t>
         </is>
       </c>
-      <c r="X39" s="3" t="inlineStr">
+      <c r="X39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">272
 </t>
@@ -6297,13 +6354,13 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">1729
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6322,19 +6379,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27281
-</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
+          <t xml:space="preserve">2781
+</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">308
 </t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2006
 </t>
         </is>
       </c>
@@ -6382,13 +6439,13 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6424,7 +6481,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">1654
 </t>
         </is>
       </c>
@@ -6440,7 +6497,7 @@
 </t>
         </is>
       </c>
-      <c r="W40" s="3" t="inlineStr">
+      <c r="W40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
@@ -6460,7 +6517,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -6483,7 +6540,7 @@
 </t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">296
 </t>
@@ -6515,16 +6572,11 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
@@ -6539,7 +6591,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6581,7 +6633,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">7205
 </t>
         </is>
       </c>
@@ -6591,7 +6643,7 @@
 </t>
         </is>
       </c>
-      <c r="V41" s="3" t="inlineStr">
+      <c r="V41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">271
 </t>
@@ -6603,7 +6655,7 @@
 </t>
         </is>
       </c>
-      <c r="X41" s="3" t="inlineStr">
+      <c r="X41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
@@ -6611,13 +6663,13 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">8411
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -6694,13 +6746,13 @@
 </t>
         </is>
       </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
@@ -6714,7 +6766,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6754,7 +6806,7 @@
 </t>
         </is>
       </c>
-      <c r="W42" s="3" t="inlineStr">
+      <c r="W42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -6762,7 +6814,7 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -6811,24 +6863,25 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">259
+</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
@@ -6856,7 +6909,7 @@
 </t>
         </is>
       </c>
-      <c r="N43" s="3" t="inlineStr">
+      <c r="N43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -6870,7 +6923,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6886,7 +6939,7 @@
 </t>
         </is>
       </c>
-      <c r="S43" s="3" t="inlineStr">
+      <c r="S43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
@@ -6900,7 +6953,7 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -6916,9 +6969,10 @@
 </t>
         </is>
       </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t>854</t>
+      <c r="X43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6929,8 +6983,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6996,19 +7049,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">0527
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
+          <t xml:space="preserve">8021
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">11278
 </t>
         </is>
       </c>
@@ -7026,13 +7079,13 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -7044,14 +7097,19 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1050816
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n"/>
+          <t xml:space="preserve">1038
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1029
+</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18205
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
@@ -7063,24 +7121,25 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 9
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463
+          <t xml:space="preserve">1463
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>633</t>
+          <t xml:space="preserve">1223
+</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1384
 </t>
         </is>
       </c>
@@ -7092,37 +7151,37 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66 8
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">12340
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">2190
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1381
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99295
+          <t xml:space="preserve">3923
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
@@ -7163,15 +7222,15 @@
 </t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">091
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -7189,7 +7248,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -7201,7 +7260,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -7223,15 +7282,15 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">953
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -7265,7 +7324,7 @@
 </t>
         </is>
       </c>
-      <c r="X46" s="3" t="inlineStr">
+      <c r="X46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">276
 </t>
@@ -7279,7 +7338,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -737,146 +728,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3513
-</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -894,146 +861,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
-</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1051,146 +994,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
-</t>
+          <t>596</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1208,146 +1127,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1365,146 +1260,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>218</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>279</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>230</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1522,146 +1393,122 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
-</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
-</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1074
-</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1345
-</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
-</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
-</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 82
-</t>
+          <t>12 82</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4870
-</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556
-</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080
-</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
-</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1395
-</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
-</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1679,146 +1526,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
-</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
-</t>
+          <t>616</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1836,8 +1659,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1847,134 +1669,112 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>266</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887
-</t>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
-</t>
+          <t>563</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
-</t>
+          <t>704</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1992,146 +1792,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>233</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>208</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>303</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2149,146 +1925,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
-</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>247</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
-</t>
+          <t>679</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
-</t>
+          <t>808</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2306,146 +2058,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
-</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2463,146 +2191,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23408
-</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>224</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">419
-</t>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>219</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
-</t>
+          <t>766</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2620,146 +2324,122 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15308
-</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542
-</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
-</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2268
-</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
-</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
-</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
-</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">763
-</t>
+          <t>763</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
-</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
-</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423
-</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2777,146 +2457,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2306
-</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2934,146 +2590,122 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>223</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3091,146 +2723,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
-</t>
+          <t>3262</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>322</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>243</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>292</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3248,146 +2856,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
-</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
-</t>
+          <t>2990</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>297</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1197
-</t>
-        </is>
-      </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>228</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
-</t>
+          <t>716</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3405,146 +2989,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
-</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>218</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18441
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3562,146 +3122,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
-</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2380
-</t>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>250</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1674
-</t>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>221</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>226</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3719,146 +3255,122 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
-</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554
-</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0962
-</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
-</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
-</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>796</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
-</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
-</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3876,146 +3388,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">053
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4033,56 +3521,47 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
-</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -4092,86 +3571,72 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4189,146 +3654,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23450
-</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4346,146 +3787,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4503,146 +3920,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2824
-</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>326</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">682
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>262</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="X28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>263</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4665,140 +4058,117 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>248</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4816,146 +4186,122 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1363
-</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11565
-</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11718
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4895
-</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
-</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
-</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337
-</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4973,146 +4319,122 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
-</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">313
-</t>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>313</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>979</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="X31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>267</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
-</t>
+          <t>823</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5130,14 +4452,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
-</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
+          <t>2635</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>290</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5147,128 +4467,107 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>279</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>698</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="X32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>291</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5286,140 +4585,117 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>241</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="Z33" s="3" t="n"/>
@@ -5438,44 +4714,37 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -5485,98 +4754,82 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>235</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="W34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>210</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5594,146 +4847,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
-</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="N35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>209</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">093
-</t>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>293</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5751,146 +4980,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11172
-</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>258</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5908,146 +5113,122 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
-</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
-</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
-</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
-</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
-</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1363
-</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3936
-</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
-</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
-</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6065,146 +5246,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">788
-</t>
+          <t>787</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6222,146 +5379,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3323
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 8
-</t>
+          <t>0 08</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
-</t>
+          <t>665</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="X39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>272</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1729
-</t>
+          <t>729</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6379,146 +5512,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
-</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2006
-</t>
+          <t>2781</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>206</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
-</t>
+          <t>654</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="W40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6536,141 +5645,118 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
-</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
+          <t>2426</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>296</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205
-</t>
+          <t>705</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>271</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="X41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>291</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8411
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6688,146 +5774,122 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
-</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>252</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="W42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6845,140 +5907,117 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
-</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">086
-</t>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>249</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="S43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>252</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>843</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -7001,8 +6040,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -7043,146 +6081,122 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14234
-</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0527
-</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8021
-</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11278
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">936
-</t>
+          <t>936</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
-</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463
-</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
-</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
-</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12340
-</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
-</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7200,146 +6214,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
-</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>276</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>785</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>422</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>219</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>0 08</t>
+          <t>01 01</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_digit_manipulation.xlsx
@@ -1463,7 +1463,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>282</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>01 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>002</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>138</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
